--- a/bakup/customers/amir mahdi.xlsx
+++ b/bakup/customers/amir mahdi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="47">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -151,6 +151,15 @@
   </si>
   <si>
     <t>1405/06/05</t>
+  </si>
+  <si>
+    <t>1405/06/07</t>
+  </si>
+  <si>
+    <t>1405/06/11</t>
+  </si>
+  <si>
+    <t>1405/06/18</t>
   </si>
 </sst>
 </file>
@@ -638,7 +647,7 @@
       </c>
       <c r="H2" s="7">
         <f>C43</f>
-        <v>220000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1107,37 +1116,55 @@
     <row r="34" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="6">
         <f t="shared" si="1"/>
-        <v>220000</v>
-      </c>
-      <c r="B34" s="6"/>
+        <v>355000</v>
+      </c>
+      <c r="B34" s="6">
+        <v>135000</v>
+      </c>
       <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="10"/>
+      <c r="D34" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="35" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="6">
         <f t="shared" si="1"/>
-        <v>220000</v>
+        <v>0</v>
       </c>
       <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="10"/>
+      <c r="C35" s="6">
+        <v>355000</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="36" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="6">
         <f t="shared" si="1"/>
-        <v>220000</v>
-      </c>
-      <c r="B36" s="6"/>
+        <v>150000</v>
+      </c>
+      <c r="B36" s="6">
+        <v>150000</v>
+      </c>
       <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="10"/>
+      <c r="D36" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="37" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6">
         <f t="shared" si="1"/>
-        <v>220000</v>
+        <v>150000</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -1147,7 +1174,7 @@
     <row r="38" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6">
         <f t="shared" si="1"/>
-        <v>220000</v>
+        <v>150000</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -1157,7 +1184,7 @@
     <row r="39" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6">
         <f t="shared" si="1"/>
-        <v>220000</v>
+        <v>150000</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -1167,7 +1194,7 @@
     <row r="40" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6">
         <f t="shared" si="1"/>
-        <v>220000</v>
+        <v>150000</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -1177,7 +1204,7 @@
     <row r="41" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6">
         <f t="shared" si="1"/>
-        <v>220000</v>
+        <v>150000</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -1187,11 +1214,11 @@
     <row r="42" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B42" s="7">
         <f>SUM(B22:B41)+B16</f>
-        <v>1728000</v>
+        <v>2013000</v>
       </c>
       <c r="C42" s="7">
         <f>SUM(C22:C41)+C16</f>
-        <v>1508000</v>
+        <v>1863000</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -1199,7 +1226,7 @@
       <c r="B43" s="7"/>
       <c r="C43" s="9">
         <f xml:space="preserve"> A41</f>
-        <v>220000</v>
+        <v>150000</v>
       </c>
       <c r="D43" s="11" t="s">
         <v>40</v>
